--- a/checklist_forms/026_guest_room_checklist--checklist_forms.xlsx
+++ b/checklist_forms/026_guest_room_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'unsatisfactory'}</t>
+          <t>unsatisfactory</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Unsatisfactory'}</t>
+          <t>Unsatisfactory</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'free_wi-fi'}</t>
+          <t>free_wi-fi</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Free Wi-Fi'}</t>
+          <t>Free Wi-Fi</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'free_parking'}</t>
+          <t>free_parking</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Free Parking'}</t>
+          <t>Free Parking</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'free_breakfast'}</t>
+          <t>free_breakfast</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Free Breakfast'}</t>
+          <t>Free Breakfast</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'in-room_mini-bar'}</t>
+          <t>in-room_mini-bar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'In-room Mini-bar'}</t>
+          <t>In-room Mini-bar</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'suite'}</t>
+          <t>suite</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Suite'}</t>
+          <t>Suite</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'double'}</t>
+          <t>double</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Double'}</t>
+          <t>Double</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'king'}</t>
+          <t>king</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'King'}</t>
+          <t>King</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'shared'}</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Shared'}</t>
+          <t>Shared</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'en-suite'}</t>
+          <t>en-suite</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'En-suite'}</t>
+          <t>En-suite</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'shared'}</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Shared'}</t>
+          <t>Shared</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'queen'}</t>
+          <t>queen</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Queen'}</t>
+          <t>Queen</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'king'}</t>
+          <t>king</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'King'}</t>
+          <t>King</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'l-shape'}</t>
+          <t>l-shape</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'L-shape'}</t>
+          <t>L-shape</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'u-shape'}</t>
+          <t>u-shape</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'U-shape'}</t>
+          <t>U-shape</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'straight'}</t>
+          <t>straight</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Straight'}</t>
+          <t>Straight</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'city_view'}</t>
+          <t>city_view</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'City View'}</t>
+          <t>City View</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'garden_view'}</t>
+          <t>garden_view</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Garden View'}</t>
+          <t>Garden View</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'clean'}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Clean'}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'needs_improvement'}</t>
+          <t>needs_improvement</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Needs Improvement'}</t>
+          <t>Needs Improvement</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'wooden'}</t>
+          <t>wooden</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Wooden'}</t>
+          <t>Wooden</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'metal'}</t>
+          <t>metal</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Metal'}</t>
+          <t>Metal</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'plastic'}</t>
+          <t>plastic</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Plastic'}</t>
+          <t>Plastic</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'modern'}</t>
+          <t>modern</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Modern'}</t>
+          <t>Modern</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'old'}</t>
+          <t>old</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Old'}</t>
+          <t>Old</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'shared'}</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Shared'}</t>
+          <t>Shared</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'modern'}</t>
+          <t>modern</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'Modern'}</t>
+          <t>Modern</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'old'}</t>
+          <t>old</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Old'}</t>
+          <t>Old</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'shared'}</t>
+          <t>shared</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'Shared'}</t>
+          <t>Shared</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'wooden'}</t>
+          <t>wooden</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Wooden'}</t>
+          <t>Wooden</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'plastic'}</t>
+          <t>plastic</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'Plastic'}</t>
+          <t>Plastic</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'metal'}</t>
+          <t>metal</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'Metal'}</t>
+          <t>Metal</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
